--- a/models/8410_DCF_Model_20260906.xlsx
+++ b/models/8410_DCF_Model_20260906.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryosuke0923\ryosuke-japanese-equity-research\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6A03940-746C-4258-8888-CFA06EC48F13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46269043-1A22-41B3-86A1-8763F6DBB080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="383">
   <si>
     <t>DISCLAIMER: This is a sample analysis for demonstration purposes only. It does not constitute investment advice.</t>
   </si>
@@ -94,7 +94,10 @@
     <t>Residual Income (主手法)</t>
   </si>
   <si>
-    <t>Comps - EV/EBITDA Median [参考・Target不算入]</t>
+    <t>Comps - EV/EBITDA Median [参考・Target不算入]（型D: 銀行に EV 倍率は使わない）</t>
+  </si>
+  <si>
+    <t>N/A</t>
   </si>
   <si>
     <t>Comps - PER Median [参考・Target不算入]</t>
@@ -601,7 +604,7 @@
     <t>Comparable Company Analysis</t>
   </si>
   <si>
-    <t>Peer prices as of 2026-09-06 (Mkt Cap / EV of peer rows are static CSV values; the subject row is live-linked to Executive Summary)</t>
+    <t>Peer prices as of 2026-09-07 (Mkt Cap / EV of peer rows are static CSV values; the subject row is live-linked to Executive Summary)</t>
   </si>
   <si>
     <t>Mkt Cap
@@ -659,9 +662,6 @@
     <t>8410.T</t>
   </si>
   <si>
-    <t>N/A</t>
-  </si>
-  <si>
     <t>Rakuten Bank</t>
   </si>
   <si>
@@ -773,13 +773,13 @@
     <t>状態</t>
   </si>
   <si>
-    <t>2026-09-06</t>
+    <t>2026-09-07</t>
   </si>
   <si>
     <t>-</t>
   </si>
   <si>
-    <t>Generated by pipeline on 2026-09-06 23:13, template rev 041abe3</t>
+    <t>Generated by pipeline on 2026-09-07 13:26, template rev 1e927a2</t>
   </si>
   <si>
     <t>初期生成（手修正なし）</t>
@@ -1004,7 +1004,7 @@
     <t>generated_at</t>
   </si>
   <si>
-    <t>2026-09-06 23:13:59</t>
+    <t>2026-09-07 13:26:01</t>
   </si>
   <si>
     <t>guidance_note</t>
@@ -1073,7 +1073,7 @@
     <t>template_rev</t>
   </si>
   <si>
-    <t>041abe3</t>
+    <t>1e927a2</t>
   </si>
   <si>
     <t>ticker</t>
@@ -1457,7 +1457,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1554,8 +1554,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1988,7 +1986,7 @@
         <v>-3.8235294117647062E-2</v>
       </c>
     </row>
-    <row r="17" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
         <v>18</v>
       </c>
@@ -2001,7 +1999,7 @@
         <v>0.11176470588235295</v>
       </c>
     </row>
-    <row r="18" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B18" t="s">
         <v>19</v>
       </c>
@@ -2010,7 +2008,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="19" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" t="s">
         <v>20</v>
       </c>
@@ -2019,23 +2017,17 @@
         <v>200</v>
       </c>
     </row>
-    <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="70" t="s">
+    <row r="20" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="72" t="str">
-        <f>'Comps Analysis'!C27</f>
-        <v>INVALID (n&lt;3)</v>
-      </c>
-      <c r="D20" s="73">
-        <f>IF(ISNUMBER(C18),(C18-C9)/C9,"N/A")</f>
-        <v>-0.48823529411764705</v>
-      </c>
-      <c r="E20" s="70"/>
-    </row>
-    <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C21" s="11">
         <f>'Comps Analysis'!C28</f>
@@ -2046,69 +2038,68 @@
         <v>-0.41176470588235292</v>
       </c>
     </row>
-    <row r="22" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" ht="14" x14ac:dyDescent="0.3">
       <c r="B22" s="1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C23" s="6" t="str">
         <f>IF(COUNT(C16:C17)=0,"N/A",MIN(C16:C17)&amp;" - "&amp;MAX(C16:C17))</f>
         <v>327 - 378</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:4" ht="14" x14ac:dyDescent="0.3">
       <c r="B25" s="8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" ht="14" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="2:5" ht="14" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" ht="14" x14ac:dyDescent="0.3">
       <c r="B30" s="8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C30" s="9"/>
       <c r="D30" s="9"/>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="B1:E1"/>
-    <mergeCell ref="B20:E20"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2171,7 +2162,7 @@
     </row>
     <row r="9" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="48">
         <f>DDM!C$9</f>
@@ -2180,7 +2171,7 @@
     </row>
     <row r="10" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C10" s="48">
         <f>DDM!C$12</f>
@@ -2194,24 +2185,24 @@
     </row>
     <row r="13" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="C13" s="54" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" s="54" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E13" s="54" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F13" s="54" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G13" s="54" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="14" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C14" s="65">
         <v>6.0999999999999999E-2</v>
@@ -2240,19 +2231,19 @@
     <row r="17" spans="2:7" ht="14" x14ac:dyDescent="0.3">
       <c r="B17" s="4"/>
       <c r="C17" s="66" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D17" s="66" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E17" s="66" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F17" s="66" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G17" s="66" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="14" x14ac:dyDescent="0.3">
@@ -2985,28 +2976,28 @@
   <sheetData>
     <row r="2" spans="2:5" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5">
         <v>197877</v>
@@ -3020,7 +3011,7 @@
     </row>
     <row r="7" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C7" s="5">
         <v>54594</v>
@@ -3034,7 +3025,7 @@
     </row>
     <row r="8" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="5">
         <f>C6-C7</f>
@@ -3051,7 +3042,7 @@
     </row>
     <row r="9" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C9" s="7">
         <f>C8/C6</f>
@@ -3068,7 +3059,7 @@
     </row>
     <row r="10" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C10" s="5">
         <v>112757</v>
@@ -3082,7 +3073,7 @@
     </row>
     <row r="11" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" s="5">
         <v>30526</v>
@@ -3096,7 +3087,7 @@
     </row>
     <row r="12" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="5">
         <v>31970</v>
@@ -3110,7 +3101,7 @@
     </row>
     <row r="13" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C13" s="7">
         <f>C11/C6</f>
@@ -3127,7 +3118,7 @@
     </row>
     <row r="14" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" s="7">
         <f>C12/C6</f>
@@ -3144,10 +3135,10 @@
     </row>
     <row r="15" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D15" s="7">
         <f>(D6-C6)/C6</f>
@@ -3160,10 +3151,10 @@
     </row>
     <row r="16" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" t="s">
         <v>49</v>
-      </c>
-      <c r="C16" t="s">
-        <v>48</v>
       </c>
       <c r="D16" s="7">
         <f>(D11-C11)/C11</f>
@@ -3176,12 +3167,12 @@
     </row>
     <row r="18" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="19" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" s="5">
         <v>100751</v>
@@ -3195,7 +3186,7 @@
     </row>
     <row r="20" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C20" s="5">
         <v>17739</v>
@@ -3209,7 +3200,7 @@
     </row>
     <row r="21" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B21" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C21" s="5">
         <f>C19-C20</f>
@@ -3226,7 +3217,7 @@
     </row>
     <row r="22" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C22" s="7">
         <f>C21/C6</f>
@@ -3243,7 +3234,7 @@
     </row>
     <row r="23" spans="2:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C23" s="7">
         <f>C20/C6</f>
@@ -3260,12 +3251,12 @@
     </row>
     <row r="25" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C26" s="5">
         <v>988721</v>
@@ -3279,7 +3270,7 @@
     </row>
     <row r="27" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C27" s="5">
         <v>65000</v>
@@ -3293,7 +3284,7 @@
     </row>
     <row r="28" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C28" s="5">
         <f>C27-C26</f>
@@ -3310,7 +3301,7 @@
     </row>
     <row r="30" spans="2:5" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -3334,17 +3325,17 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="2:7" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
@@ -3354,7 +3345,7 @@
     </row>
     <row r="5" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C5" s="7">
         <v>0.155</v>
@@ -3362,7 +3353,7 @@
     </row>
     <row r="6" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C6" s="7">
         <v>0.25</v>
@@ -3370,7 +3361,7 @@
     </row>
     <row r="7" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C7" s="7">
         <v>2.9700000000000001E-2</v>
@@ -3378,7 +3369,7 @@
     </row>
     <row r="8" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" s="12">
         <v>0.62639999999999996</v>
@@ -3386,7 +3377,7 @@
     </row>
     <row r="9" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C9" s="7">
         <v>6.5000000000000002E-2</v>
@@ -3394,7 +3385,7 @@
     </row>
     <row r="10" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" s="7">
         <v>0.01</v>
@@ -3402,7 +3393,7 @@
     </row>
     <row r="11" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="7">
         <v>0.01</v>
@@ -3410,7 +3401,7 @@
     </row>
     <row r="12" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="13">
         <v>0</v>
@@ -3418,7 +3409,7 @@
     </row>
     <row r="13" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" s="7">
         <v>0.01</v>
@@ -3426,7 +3417,7 @@
     </row>
     <row r="14" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" s="14">
         <v>7</v>
@@ -3434,7 +3425,7 @@
     </row>
     <row r="15" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C15" s="15">
         <v>1167997856</v>
@@ -3442,7 +3433,7 @@
     </row>
     <row r="16" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" s="5">
         <v>0</v>
@@ -3450,7 +3441,7 @@
     </row>
     <row r="17" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C17" s="5">
         <v>220025</v>
@@ -3458,7 +3449,7 @@
     </row>
     <row r="18" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C18" s="7">
         <v>0.13900000000000001</v>
@@ -3466,7 +3457,7 @@
     </row>
     <row r="19" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C19" s="12">
         <v>1</v>
@@ -3474,7 +3465,7 @@
     </row>
     <row r="20" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C20" s="5">
         <v>220025</v>
@@ -3482,7 +3473,7 @@
     </row>
     <row r="22" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -3492,7 +3483,7 @@
     </row>
     <row r="23" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C23" s="16">
         <f>C7+C8*C9+C10</f>
@@ -3501,7 +3492,7 @@
     </row>
     <row r="24" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C24" s="16">
         <f>1/(1+C12)</f>
@@ -3510,7 +3501,7 @@
     </row>
     <row r="25" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="16">
         <f>C12/(1+C12)</f>
@@ -3519,7 +3510,7 @@
     </row>
     <row r="26" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26" s="16">
         <f>C23*C24+C11*C25</f>
@@ -3528,10 +3519,10 @@
     </row>
     <row r="27" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27" s="17" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D27" s="6">
         <f>MATCH(C27,B69:B73,0)</f>
@@ -3540,7 +3531,7 @@
     </row>
     <row r="28" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C28" s="9"/>
       <c r="D28" s="9"/>
@@ -3550,24 +3541,24 @@
     </row>
     <row r="29" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C29" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F29" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G29" s="10" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="30" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" s="18">
         <f>CHOOSE($D$27,C69,C70,C71,C72,C73)</f>
@@ -3592,7 +3583,7 @@
     </row>
     <row r="31" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B31" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C31" s="18">
         <f>CHOOSE($D$27,C76,C77,C78,C79,C80)</f>
@@ -3617,7 +3608,7 @@
     </row>
     <row r="32" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C32" s="18">
         <f>CHOOSE($D$27,C83,C84,C85,C86,C87)</f>
@@ -3642,7 +3633,7 @@
     </row>
     <row r="33" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C33" s="5">
         <f>C17*(1+C30)</f>
@@ -3667,7 +3658,7 @@
     </row>
     <row r="34" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C34" s="5">
         <f>C33*C31</f>
@@ -3692,7 +3683,7 @@
     </row>
     <row r="35" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C35" s="19">
         <f>C33-C34</f>
@@ -3717,7 +3708,7 @@
     </row>
     <row r="36" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C36" s="7">
         <f>C35/C33</f>
@@ -3742,7 +3733,7 @@
     </row>
     <row r="37" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C37" s="5">
         <f>C33*C32</f>
@@ -3767,7 +3758,7 @@
     </row>
     <row r="38" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C38" s="7">
         <f>(C35-C37)/C33</f>
@@ -3792,7 +3783,7 @@
     </row>
     <row r="39" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C39" s="19">
         <f>C35-C37</f>
@@ -3817,7 +3808,7 @@
     </row>
     <row r="40" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C40" s="5">
         <f>MAX(0,C39*C6)</f>
@@ -3842,7 +3833,7 @@
     </row>
     <row r="41" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C41" s="19">
         <f>C39-C40</f>
@@ -3867,7 +3858,7 @@
     </row>
     <row r="42" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C42" s="5">
         <v>32000</v>
@@ -3887,7 +3878,7 @@
     </row>
     <row r="43" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C43" s="5">
         <v>38000</v>
@@ -3907,7 +3898,7 @@
     </row>
     <row r="44" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C44" s="5">
         <f>'NWC Schedule'!D19</f>
@@ -3932,7 +3923,7 @@
     </row>
     <row r="45" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C45" s="20">
         <f>C41+C42-C43-C44</f>
@@ -3957,7 +3948,7 @@
     </row>
     <row r="46" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C46" s="21">
         <f>1/(1+C26)^(C19+0)</f>
@@ -3982,7 +3973,7 @@
     </row>
     <row r="47" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C47" s="19">
         <f>C45*C46</f>
@@ -4007,7 +3998,7 @@
     </row>
     <row r="49" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="22" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C49" s="23"/>
       <c r="D49" s="23"/>
@@ -4017,7 +4008,7 @@
     </row>
     <row r="50" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C50" s="5">
         <f>SUM(C47:G47)</f>
@@ -4026,7 +4017,7 @@
     </row>
     <row r="51" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C51" s="5">
         <f>G45*(1+C13)/(C26-C13)</f>
@@ -4035,7 +4026,7 @@
     </row>
     <row r="52" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C52" s="5">
         <f>C51*G46</f>
@@ -4044,7 +4035,7 @@
     </row>
     <row r="53" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C53" s="5">
         <f>C50+C52</f>
@@ -4053,7 +4044,7 @@
     </row>
     <row r="54" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C54" s="5">
         <f>C53-C16</f>
@@ -4062,7 +4053,7 @@
     </row>
     <row r="55" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C55" s="24">
         <f>ROUND(C54*1000000/C15,0)</f>
@@ -4071,7 +4062,7 @@
     </row>
     <row r="57" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B57" s="22" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C57" s="23"/>
       <c r="D57" s="23"/>
@@ -4081,7 +4072,7 @@
     </row>
     <row r="58" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C58" s="5">
         <f>C50</f>
@@ -4090,7 +4081,7 @@
     </row>
     <row r="59" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C59" s="5">
         <f>G39+G42</f>
@@ -4099,7 +4090,7 @@
     </row>
     <row r="60" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C60" s="5">
         <f>C59*C14</f>
@@ -4108,7 +4099,7 @@
     </row>
     <row r="61" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B61" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C61" s="5">
         <f>C60*G46</f>
@@ -4117,7 +4108,7 @@
     </row>
     <row r="62" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C62" s="5">
         <f>C58+C61</f>
@@ -4126,7 +4117,7 @@
     </row>
     <row r="63" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C63" s="5">
         <f>C62-C16</f>
@@ -4135,7 +4126,7 @@
     </row>
     <row r="64" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C64" s="24">
         <f>ROUND(C63*1000000/C15,0)</f>
@@ -4144,7 +4135,7 @@
     </row>
     <row r="66" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="22" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C66" s="23"/>
       <c r="D66" s="23"/>
@@ -4154,29 +4145,29 @@
     </row>
     <row r="67" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C67" s="25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D67" s="25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E67" s="25" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G67" s="25" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="68" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C69" s="26">
         <v>0.05</v>
@@ -4196,7 +4187,7 @@
     </row>
     <row r="70" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C70" s="26">
         <v>0.09</v>
@@ -4216,7 +4207,7 @@
     </row>
     <row r="71" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C71" s="26">
         <v>7.0000000000000007E-2</v>
@@ -4236,7 +4227,7 @@
     </row>
     <row r="72" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C72" s="26">
         <v>0.02</v>
@@ -4256,7 +4247,7 @@
     </row>
     <row r="73" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C73" s="26">
         <v>-0.02</v>
@@ -4276,12 +4267,12 @@
     </row>
     <row r="75" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="76" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C76" s="26">
         <v>0.26500000000000001</v>
@@ -4301,7 +4292,7 @@
     </row>
     <row r="77" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C77" s="26">
         <v>0.26</v>
@@ -4321,7 +4312,7 @@
     </row>
     <row r="78" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C78" s="26">
         <v>0.26500000000000001</v>
@@ -4341,7 +4332,7 @@
     </row>
     <row r="79" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C79" s="26">
         <v>0.27500000000000002</v>
@@ -4361,7 +4352,7 @@
     </row>
     <row r="80" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C80" s="26">
         <v>0.28499999999999998</v>
@@ -4381,12 +4372,12 @@
     </row>
     <row r="82" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="83" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C83" s="26">
         <v>0.61</v>
@@ -4406,7 +4397,7 @@
     </row>
     <row r="84" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C84" s="26">
         <v>0.60499999999999998</v>
@@ -4426,7 +4417,7 @@
     </row>
     <row r="85" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C85" s="26">
         <v>0.61</v>
@@ -4446,7 +4437,7 @@
     </row>
     <row r="86" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C86" s="26">
         <v>0.61499999999999999</v>
@@ -4466,7 +4457,7 @@
     </row>
     <row r="87" spans="2:7" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C87" s="26">
         <v>0.625</v>
@@ -4510,17 +4501,17 @@
   <sheetData>
     <row r="2" spans="2:9" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C5" s="9"/>
       <c r="D5" s="9"/>
@@ -4532,7 +4523,7 @@
     </row>
     <row r="6" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C6" s="15">
         <f>'Executive Summary'!C9</f>
@@ -4541,7 +4532,7 @@
     </row>
     <row r="7" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C7" s="15">
         <f>'DCF Model'!C15</f>
@@ -4550,7 +4541,7 @@
     </row>
     <row r="8" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C8" s="5">
         <f>C6*C7/1000000</f>
@@ -4559,7 +4550,7 @@
     </row>
     <row r="9" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C9" s="5">
         <f>'DCF Model'!C16</f>
@@ -4568,7 +4559,7 @@
     </row>
     <row r="10" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C10" s="5">
         <f>C8+C9</f>
@@ -4577,7 +4568,7 @@
     </row>
     <row r="11" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C11" s="16">
         <f>'DCF Model'!C26</f>
@@ -4586,7 +4577,7 @@
     </row>
     <row r="12" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" s="16">
         <f>'DCF Model'!C13</f>
@@ -4595,7 +4586,7 @@
     </row>
     <row r="13" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C13" s="16">
         <f>'DCF Model'!C6</f>
@@ -4604,7 +4595,7 @@
     </row>
     <row r="14" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C14" s="27">
         <v>30165</v>
@@ -4612,7 +4603,7 @@
     </row>
     <row r="15" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C15" s="27">
         <v>30526</v>
@@ -4620,7 +4611,7 @@
     </row>
     <row r="16" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C16" s="5">
         <f>'DCF Model'!G33</f>
@@ -4629,7 +4620,7 @@
     </row>
     <row r="17" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C17" s="5">
         <f>'DCF Model'!C53</f>
@@ -4638,7 +4629,7 @@
     </row>
     <row r="18" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C18" s="26">
         <v>0.15426755004371401</v>
@@ -4646,7 +4637,7 @@
     </row>
     <row r="19" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C19" s="5">
         <f>C10-C17</f>
@@ -4655,7 +4646,7 @@
     </row>
     <row r="20" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="15">
         <f>IFERROR(ROUND(C19*1000000/C7,0),"N/A")</f>
@@ -4664,7 +4655,7 @@
     </row>
     <row r="22" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C22" s="9"/>
       <c r="D22" s="9"/>
@@ -4676,12 +4667,12 @@
     </row>
     <row r="23" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C24" s="5">
         <f>C10*(C11-C12)</f>
@@ -4690,7 +4681,7 @@
     </row>
     <row r="25" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C25" s="5">
         <f>IFERROR(C24/(1-C13),"N/A")</f>
@@ -4699,7 +4690,7 @@
     </row>
     <row r="26" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C26" s="14">
         <f>IFERROR(C25/C15,"N/A")</f>
@@ -4708,7 +4699,7 @@
     </row>
     <row r="27" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C27" s="14">
         <f>IFERROR(C25/C14,"N/A")</f>
@@ -4717,7 +4708,7 @@
     </row>
     <row r="28" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C28" s="7">
         <f>IFERROR(C25/C16,"N/A")</f>
@@ -4726,7 +4717,7 @@
     </row>
     <row r="29" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C29" s="5">
         <f>IFERROR(C25/C18,"N/A")</f>
@@ -4735,7 +4726,7 @@
     </row>
     <row r="32" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C32" s="9"/>
       <c r="D32" s="9"/>
@@ -4747,20 +4738,20 @@
     </row>
     <row r="33" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="36" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B36" s="28" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C36" s="28" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D36" s="29">
         <f>'DCF Model'!C26-0.02</f>
@@ -4785,12 +4776,12 @@
     </row>
     <row r="37" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B37" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B38" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C38" s="30">
         <v>3</v>
@@ -4818,7 +4809,7 @@
     </row>
     <row r="39" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B39" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C39" s="30">
         <v>5</v>
@@ -4846,7 +4837,7 @@
     </row>
     <row r="40" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C40" s="30">
         <v>7</v>
@@ -4874,7 +4865,7 @@
     </row>
     <row r="41" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C41" s="30">
         <v>10</v>
@@ -4902,12 +4893,12 @@
     </row>
     <row r="42" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C43" s="30">
         <v>3</v>
@@ -4935,7 +4926,7 @@
     </row>
     <row r="44" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C44" s="30">
         <v>5</v>
@@ -4963,7 +4954,7 @@
     </row>
     <row r="45" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C45" s="30">
         <v>7</v>
@@ -4991,7 +4982,7 @@
     </row>
     <row r="46" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B46" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C46" s="30">
         <v>10</v>
@@ -5019,7 +5010,7 @@
     </row>
     <row r="47" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B47" s="22" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C47" s="23"/>
       <c r="D47" s="23"/>
@@ -5031,7 +5022,7 @@
     </row>
     <row r="48" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B48" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C48" s="30">
         <v>3</v>
@@ -5059,7 +5050,7 @@
     </row>
     <row r="49" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C49" s="30">
         <v>5</v>
@@ -5087,7 +5078,7 @@
     </row>
     <row r="50" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C50" s="30">
         <v>7</v>
@@ -5115,7 +5106,7 @@
     </row>
     <row r="51" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C51" s="30">
         <v>10</v>
@@ -5143,7 +5134,7 @@
     </row>
     <row r="52" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="22" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C52" s="23"/>
       <c r="D52" s="23"/>
@@ -5155,7 +5146,7 @@
     </row>
     <row r="53" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C53" s="30">
         <v>3</v>
@@ -5183,7 +5174,7 @@
     </row>
     <row r="54" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C54" s="30">
         <v>5</v>
@@ -5211,7 +5202,7 @@
     </row>
     <row r="55" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C55" s="30">
         <v>7</v>
@@ -5239,7 +5230,7 @@
     </row>
     <row r="56" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C56" s="30">
         <v>10</v>
@@ -5267,7 +5258,7 @@
     </row>
     <row r="58" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B58" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C58" s="9"/>
       <c r="D58" s="9"/>
@@ -5279,12 +5270,12 @@
     </row>
     <row r="59" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="60" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C60" s="5">
         <f>F49</f>
@@ -5293,13 +5284,13 @@
     </row>
     <row r="62" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="28" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C62" s="28" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D62" s="28" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="63" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
@@ -5330,7 +5321,7 @@
     </row>
     <row r="65" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C65" s="5">
         <f>IFERROR($C$60/$C$18,"N/A")</f>
@@ -5369,7 +5360,7 @@
     </row>
     <row r="69" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="8" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C69" s="9"/>
       <c r="D69" s="9"/>
@@ -5381,7 +5372,7 @@
     </row>
     <row r="70" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C70" s="14">
         <f>IFERROR(C10/'Comps Analysis'!G5,"N/A")</f>
@@ -5390,7 +5381,7 @@
     </row>
     <row r="71" spans="2:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C71" s="14">
         <f>IFERROR(C10/'Comps Analysis'!F5,"N/A")</f>
@@ -5399,7 +5390,7 @@
     </row>
     <row r="72" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C72" s="14">
         <f>IFERROR(C10/(C25+'DCF Model'!G42),"N/A")</f>
@@ -5408,7 +5399,7 @@
     </row>
     <row r="73" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C73" s="14">
         <f>IFERROR(C10/(C60+'DCF Model'!G42),"N/A")</f>
@@ -5417,7 +5408,7 @@
     </row>
     <row r="74" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C74" s="14" t="str">
         <f>IFERROR('Comps Analysis'!D16,"N/A")</f>
@@ -5426,12 +5417,12 @@
     </row>
     <row r="75" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="77" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="22" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C77" s="23"/>
       <c r="D77" s="23"/>
@@ -5474,35 +5465,35 @@
   <sheetData>
     <row r="2" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="8" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C4" s="32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D4" s="32" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E4" s="32" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F4" s="32" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H4" s="32" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C5" s="34">
         <f>C18/C9</f>
@@ -5531,53 +5522,53 @@
     </row>
     <row r="6" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E6" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F6" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G6" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H6" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E7" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F7" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G7" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H7" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B8" s="8" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
@@ -5588,7 +5579,7 @@
     </row>
     <row r="9" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="33" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C9" s="36">
         <v>220025</v>
@@ -5616,30 +5607,30 @@
     </row>
     <row r="10" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E10" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F10" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G10" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H10" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="8" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
@@ -5650,122 +5641,122 @@
     </row>
     <row r="12" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E12" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F12" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G12" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E13" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F13" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G13" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E14" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F14" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G14" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="15" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D15" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E15" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F15" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G15" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H15" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D16" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E16" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F16" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G16" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H16" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="22" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C17" s="23"/>
       <c r="D17" s="23"/>
@@ -5776,7 +5767,7 @@
     </row>
     <row r="18" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="33" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C18" s="20">
         <v>0</v>
@@ -5804,10 +5795,10 @@
     </row>
     <row r="19" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="33" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C19" s="37" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D19" s="24">
         <f>D18-C18</f>
@@ -5832,7 +5823,7 @@
     </row>
     <row r="22" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B22" s="22" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C22" s="23"/>
       <c r="D22" s="23"/>
@@ -5843,29 +5834,29 @@
     </row>
     <row r="23" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="25" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H23" s="25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D25" s="26">
         <v>0</v>
@@ -5885,7 +5876,7 @@
     </row>
     <row r="26" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B26" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D26" s="26">
         <v>0</v>
@@ -5905,7 +5896,7 @@
     </row>
     <row r="27" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D27" s="26">
         <v>0</v>
@@ -5925,7 +5916,7 @@
     </row>
     <row r="28" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D28" s="26">
         <v>0</v>
@@ -5945,7 +5936,7 @@
     </row>
     <row r="29" spans="2:8" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B29" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D29" s="26">
         <v>0</v>
@@ -5986,12 +5977,12 @@
   <sheetData>
     <row r="2" spans="2:17" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="2:17" ht="28" customHeight="1" x14ac:dyDescent="0.3">
@@ -6002,54 +5993,54 @@
         <v>5</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G4" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M4" s="10" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N4" s="10" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="O4" s="10" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="P4" s="10" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="Q4" s="10" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" spans="2:17" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C5" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D5" s="38">
         <f>'Executive Summary'!C9*C23/1000000</f>
@@ -6072,10 +6063,10 @@
         <v>13476</v>
       </c>
       <c r="J5" s="39" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="K5" s="39" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="L5" s="39">
         <f>IFERROR(D5/I5,"")</f>
@@ -6251,10 +6242,10 @@
         <v>216</v>
       </c>
       <c r="D15" s="42" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="E15" s="39" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="F15" s="39">
         <f>PERCENTILE(L6:L8,0.25)</f>
@@ -6278,10 +6269,10 @@
         <v>217</v>
       </c>
       <c r="D16" s="42" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="E16" s="39" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="F16" s="39">
         <f>MEDIAN(L6:L8)</f>
@@ -6305,10 +6296,10 @@
         <v>218</v>
       </c>
       <c r="D17" s="42" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="E17" s="39" t="s">
-        <v>207</v>
+        <v>22</v>
       </c>
       <c r="F17" s="39">
         <f>PERCENTILE(L6:L8,0.75)</f>
@@ -6370,7 +6361,7 @@
     </row>
     <row r="24" spans="2:9" ht="14" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B24" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C24" s="5">
         <v>0</v>
@@ -7501,7 +7492,7 @@
         <v>346</v>
       </c>
       <c r="C62" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -7540,7 +7531,7 @@
     </row>
     <row r="6" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" s="48">
         <f>'DCF Model'!C7</f>
@@ -7549,7 +7540,7 @@
     </row>
     <row r="7" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" s="49">
         <f>'DCF Model'!C8</f>
@@ -7558,7 +7549,7 @@
     </row>
     <row r="8" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" s="48">
         <f>'DCF Model'!C9</f>
@@ -7567,7 +7558,7 @@
     </row>
     <row r="9" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="48">
         <f>'DCF Model'!C23</f>
@@ -7594,7 +7585,7 @@
     </row>
     <row r="12" spans="2:3" ht="14" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" s="52">
         <v>0.01</v>
@@ -7616,19 +7607,19 @@
     </row>
     <row r="17" spans="2:11" ht="14" x14ac:dyDescent="0.3">
       <c r="C17" s="54" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D17" s="54" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E17" s="54" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F17" s="54" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G17" s="54" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" spans="2:11" ht="14" x14ac:dyDescent="0.3">
@@ -7656,7 +7647,7 @@
     </row>
     <row r="19" spans="2:11" ht="14" x14ac:dyDescent="0.3">
       <c r="B19" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C19" s="56">
         <f>1/(1+$C$9)^1</f>
@@ -7729,7 +7720,7 @@
     </row>
     <row r="25" spans="2:11" ht="14" x14ac:dyDescent="0.3">
       <c r="B25" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C25" s="49">
         <f>C24*G19</f>
